--- a/TABLAS/Tablas_suplementarias_trabajo.xlsx
+++ b/TABLAS/Tablas_suplementarias_trabajo.xlsx
@@ -414,12 +414,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7 756</t>
+          <t>7 735</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>7 748</t>
+          <t>7 727</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -429,17 +429,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>9 232,3</t>
+          <t>9 189,0</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0,105</t>
+          <t>0,125</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0,2071</t>
+          <t>0,2077</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -449,7 +449,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7,2</t>
+          <t>6,9</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -466,22 +466,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11 611</t>
+          <t>11 597</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>11 589</t>
+          <t>11 583</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>594</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>14 291,0</t>
+          <t>14 286,2</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -491,22 +491,22 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0,1820</t>
+          <t>0,1825</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0,2005</t>
+          <t>0,2006</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>9,2</t>
+          <t>9,0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>98,8</t>
+          <t>99,5</t>
         </is>
       </c>
     </row>
@@ -518,12 +518,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5 204</t>
+          <t>5 203</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>5 204</t>
+          <t>5 203</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -538,12 +538,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0,810</t>
+          <t>0,809</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0,2031</t>
+          <t>0,2022</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -553,7 +553,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8,9</t>
+          <t>9,3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -570,47 +570,47 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4 389</t>
+          <t>4 388</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4 380</t>
+          <t>4 382</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>558</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5 615,5</t>
+          <t>5 614,0</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0,672</t>
+          <t>0,649</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0,2749</t>
+          <t>0,2739</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0,2855</t>
+          <t>0,2854</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3,7</t>
+          <t>4,0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>98,8</t>
+          <t>99,5</t>
         </is>
       </c>
     </row>
@@ -622,37 +622,37 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4 389</t>
+          <t>4 388</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4 380</t>
+          <t>4 382</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>558</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>5 872,3</t>
+          <t>5 874,7</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0,502</t>
+          <t>0,512</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0,2795</t>
+          <t>0,2794</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0,2881</t>
+          <t>0,2880</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -662,14 +662,14 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>98,8</t>
+          <t>99,5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Nota: el paso de tratamiento es idéntico bajo criterio ESH y ACC/AHA por construcción (verificado numéricamente) -- una sola fila, no dos. 'n (denominador del paso)' es el número de personas elegibles para ese paso de la cascada; 'n (modelo)' es el número efectivamente ajustado, menor cuando alguna covariable de área no cubre todos los municipios. WAIC y Phi corresponden al modelo FINAL (con covariables de área seleccionadas por WAIC+CPO), no al modelo univariado de exploración. Sensibilidad a matriz de vecindad (reina vs. torre), probada en Tratamiento (mayor Phi): WAIC 3913.2 vs 3913.5 (Δ=0.24), Phi 0.810 vs 0.808 (Δ=-0.002). WAIC: Widely Applicable Information Criterion (criterio de selección de modelos, valores menores indican mejor ajuste). Phi: fracción de la varianza espacial explicada por la estructura geográfica (modelo BYM2), de 0 a 1. RMSE: raíz del error cuadrático medio (validación cruzada espacial de 5 pliegues). BYM2: modelo espacial bayesiano Besag-York-Mollié tipo 2.</t>
+          <t>Nota: el paso de tratamiento es idéntico bajo criterio ESH y ACC/AHA por construcción (verificado numéricamente) -- una sola fila, no dos. 'n (denominador del paso)' es el número de personas elegibles para ese paso de la cascada; 'n (modelo)' es el número efectivamente ajustado, menor cuando alguna covariable de área no cubre todos los municipios. WAIC y Phi corresponden al modelo FINAL (con covariables de área seleccionadas por WAIC+CPO), no al modelo univariado de exploración. Sensibilidad a matriz de vecindad (reina vs. torre), probada en Tratamiento (mayor Phi): WAIC 3913.2 vs 3913.4 (Δ=0.24), Phi 0.809 vs 0.808 (Δ=-0.001). WAIC: Widely Applicable Information Criterion (criterio de selección de modelos, valores menores indican mejor ajuste). Phi: fracción de la varianza espacial explicada por la estructura geográfica (modelo BYM2), de 0 a 1. RMSE: raíz del error cuadrático medio (validación cruzada espacial de 5 pliegues). BYM2: modelo espacial bayesiano Besag-York-Mollié tipo 2.</t>
         </is>
       </c>
     </row>

--- a/TABLAS/Tablas_suplementarias_trabajo.xlsx
+++ b/TABLAS/Tablas_suplementarias_trabajo.xlsx
@@ -419,42 +419,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>7 727</t>
+          <t>7 735</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>589</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>9 189,0</t>
+          <t>9 297,8</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0,125</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0,2077</t>
+          <t>0,2308</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0,2231</t>
+          <t>0,2469</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6,9</t>
+          <t>6,5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>99,5</t>
+          <t>99,6</t>
         </is>
       </c>
     </row>
@@ -471,42 +471,42 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>11 583</t>
+          <t>11 597</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>596</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>14 286,2</t>
+          <t>13 911,5</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0,062</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0,1825</t>
+          <t>0,1949</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0,2006</t>
+          <t>0,2161</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>9,0</t>
+          <t>9,8</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>99,5</t>
+          <t>99,6</t>
         </is>
       </c>
     </row>
@@ -533,27 +533,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3 913,2</t>
+          <t>4 205,8</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0,809</t>
+          <t>0,453</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0,2022</t>
+          <t>0,2218</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0,2231</t>
+          <t>0,2460</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>9,3</t>
+          <t>9,8</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5 614,0</t>
+          <t>5 664,5</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0,649</t>
+          <t>0,207</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0,2739</t>
+          <t>0,2928</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0,2854</t>
+          <t>0,2997</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4,0</t>
+          <t>2,3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -637,27 +637,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>5 874,7</t>
+          <t>5 886,1</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0,512</t>
+          <t>0,227</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0,2794</t>
+          <t>0,2984</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0,2880</t>
+          <t>0,3024</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3,0</t>
+          <t>1,3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -669,7 +669,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Nota: el paso de tratamiento es idéntico bajo criterio ESH y ACC/AHA por construcción (verificado numéricamente) -- una sola fila, no dos. 'n (denominador del paso)' es el número de personas elegibles para ese paso de la cascada; 'n (modelo)' es el número efectivamente ajustado, menor cuando alguna covariable de área no cubre todos los municipios. WAIC y Phi corresponden al modelo FINAL (con covariables de área seleccionadas por WAIC+CPO), no al modelo univariado de exploración. Sensibilidad a matriz de vecindad (reina vs. torre), probada en Tratamiento (mayor Phi): WAIC 3913.2 vs 3913.4 (Δ=0.24), Phi 0.809 vs 0.808 (Δ=-0.001). WAIC: Widely Applicable Information Criterion (criterio de selección de modelos, valores menores indican mejor ajuste). Phi: fracción de la varianza espacial explicada por la estructura geográfica (modelo BYM2), de 0 a 1. RMSE: raíz del error cuadrático medio (validación cruzada espacial de 5 pliegues). BYM2: modelo espacial bayesiano Besag-York-Mollié tipo 2.</t>
+          <t>Nota: el paso de tratamiento es idéntico bajo criterio ESH y ACC/AHA por construcción (verificado numéricamente) -- una sola fila, no dos. 'n (denominador del paso)' es el número de personas elegibles para ese paso de la cascada; 'n (modelo)' es el número efectivamente ajustado, menor cuando alguna covariable de área no cubre todos los municipios. WAIC y Phi corresponden al modelo FINAL ponderado (pseudo-verosimilitud con ponde_cal normalizado a media 1 dentro de cada municipio; covariables de área seleccionadas por ΔWAIC&lt;=-2, mejora concordante del log-CPO y cero fallos CPO), no al modelo univariado de exploración. Sensibilidad a matriz de vecindad (reina vs. torre), probada en Tratamiento (mayor Phi): WAIC 4205.8 vs 4205.9 (Δ=0.14), Phi 0.453 vs 0.452 (Δ=-0.001). WAIC: Widely Applicable Information Criterion (criterio de selección de modelos, valores menores indican mejor ajuste). Phi: fracción de la varianza espacial explicada por la estructura geográfica (modelo BYM2), de 0 a 1. RMSE: raíz del error cuadrático medio (validación cruzada espacial de 5 pliegues con observados y predicciones agregados mediante ponde_cal). BYM2: modelo espacial bayesiano Besag-York-Mollié tipo 2.</t>
         </is>
       </c>
     </row>
